--- a/T3/2026　VDM管理指標　（　月） QLTB-T3.xlsx
+++ b/T3/2026　VDM管理指標　（　月） QLTB-T3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\VDM-FSVR\Thiet Bi-設管\3. QUAN LY DAT HANG-発注管理\15.GIAO DUC 教育\14.GCN - GOI COKHI\NAM2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code_cokhi\Bao_Cao_MMK_KPI\T3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053F5B76-CE68-42E7-9D6D-470CC7AB7B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315D30E6-A868-408D-9FCB-B743E15021FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="指標２(外作)" sheetId="23" r:id="rId1"/>
@@ -4235,6 +4235,42 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="86" xfId="7" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="88" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="89" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="90" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="92" xfId="7" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="94" xfId="7" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="95" xfId="7" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="96" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="4" borderId="91" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="4" borderId="33" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="38" fontId="11" fillId="0" borderId="68" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4244,6 +4280,132 @@
     <xf numFmtId="38" fontId="11" fillId="0" borderId="69" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="23" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="24" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="25" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="68" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="67" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="69" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="68" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="67" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="69" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="34" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="35" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="36" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="24" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="27" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="24" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="24" fillId="0" borderId="24" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="24" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="24" fillId="0" borderId="68" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="24" fillId="0" borderId="67" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="24" fillId="0" borderId="69" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="3" borderId="23" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="3" borderId="24" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="3" borderId="25" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="24" fillId="0" borderId="23" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="24" fillId="0" borderId="24" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="24" fillId="0" borderId="25" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="38" fontId="11" fillId="0" borderId="84" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4253,131 +4415,41 @@
     <xf numFmtId="38" fontId="11" fillId="0" borderId="83" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="23" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="24" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="25" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="24" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="68" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="67" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="69" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="3" borderId="23" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="3" borderId="24" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="3" borderId="25" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="26" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="27" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="24" fillId="0" borderId="23" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="24" fillId="0" borderId="24" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="24" fillId="0" borderId="25" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="24" fillId="0" borderId="23" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="24" fillId="0" borderId="24" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="24" fillId="0" borderId="25" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="24" fillId="0" borderId="68" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="24" fillId="0" borderId="67" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="24" fillId="0" borderId="69" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="34" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="35" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="11" fillId="0" borderId="36" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="68" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="67" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="69" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4397,18 +4469,6 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="53" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4426,66 +4486,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="86" xfId="7" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="88" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="89" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="90" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="92" xfId="7" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="94" xfId="7" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="95" xfId="7" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="96" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="4" borderId="91" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="4" borderId="33" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -8708,7 +8708,7 @@
                   <c:v>187021</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -11776,8 +11776,8 @@
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:29" s="4" customFormat="1" ht="13.5" customHeight="1" thickTop="1">
-      <c r="A10" s="275"/>
-      <c r="B10" s="264" t="s">
+      <c r="A10" s="260"/>
+      <c r="B10" s="280" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="26" t="s">
@@ -11850,8 +11850,8 @@
       <c r="AC10" s="203"/>
     </row>
     <row r="11" spans="1:29" ht="13.5" customHeight="1">
-      <c r="A11" s="276"/>
-      <c r="B11" s="265"/>
+      <c r="A11" s="261"/>
+      <c r="B11" s="281"/>
       <c r="C11" s="28" t="s">
         <v>16</v>
       </c>
@@ -11922,8 +11922,8 @@
       <c r="AC11" s="1"/>
     </row>
     <row r="12" spans="1:29" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A12" s="277"/>
-      <c r="B12" s="266"/>
+      <c r="A12" s="262"/>
+      <c r="B12" s="282"/>
       <c r="C12" s="44" t="s">
         <v>17</v>
       </c>
@@ -11994,10 +11994,10 @@
       <c r="AC12" s="1"/>
     </row>
     <row r="13" spans="1:29" ht="13.5" customHeight="1">
-      <c r="A13" s="258" t="s">
+      <c r="A13" s="263" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="243" t="s">
+      <c r="B13" s="252" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -12058,8 +12058,8 @@
       <c r="AC13" s="1"/>
     </row>
     <row r="14" spans="1:29" ht="13.5" customHeight="1">
-      <c r="A14" s="247"/>
-      <c r="B14" s="243"/>
+      <c r="A14" s="264"/>
+      <c r="B14" s="252"/>
       <c r="C14" s="28" t="s">
         <v>16</v>
       </c>
@@ -12118,8 +12118,8 @@
       <c r="AC14" s="1"/>
     </row>
     <row r="15" spans="1:29" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A15" s="259"/>
-      <c r="B15" s="243"/>
+      <c r="A15" s="265"/>
+      <c r="B15" s="252"/>
       <c r="C15" s="46" t="s">
         <v>17</v>
       </c>
@@ -12186,10 +12186,10 @@
       <c r="AC15" s="1"/>
     </row>
     <row r="16" spans="1:29" ht="13.5" customHeight="1">
-      <c r="A16" s="246" t="s">
+      <c r="A16" s="266" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="267" t="s">
+      <c r="B16" s="271" t="s">
         <v>36</v>
       </c>
       <c r="C16" s="33" t="s">
@@ -12249,8 +12249,8 @@
       <c r="AC16" s="1"/>
     </row>
     <row r="17" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A17" s="247"/>
-      <c r="B17" s="245"/>
+      <c r="A17" s="264"/>
+      <c r="B17" s="272"/>
       <c r="C17" s="36" t="s">
         <v>16</v>
       </c>
@@ -12308,8 +12308,8 @@
       <c r="AC17" s="1"/>
     </row>
     <row r="18" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A18" s="248"/>
-      <c r="B18" s="268"/>
+      <c r="A18" s="267"/>
+      <c r="B18" s="273"/>
       <c r="C18" s="46" t="s">
         <v>17</v>
       </c>
@@ -12377,10 +12377,10 @@
       <c r="AC18" s="1"/>
     </row>
     <row r="19" spans="1:31" s="6" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A19" s="246" t="s">
+      <c r="A19" s="266" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="249" t="s">
+      <c r="B19" s="274" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="38" t="s">
@@ -12438,8 +12438,8 @@
       <c r="AC19" s="20"/>
     </row>
     <row r="20" spans="1:31" s="6" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A20" s="247"/>
-      <c r="B20" s="250"/>
+      <c r="A20" s="264"/>
+      <c r="B20" s="275"/>
       <c r="C20" s="40" t="s">
         <v>16</v>
       </c>
@@ -12495,8 +12495,8 @@
       <c r="AC20" s="20"/>
     </row>
     <row r="21" spans="1:31" s="6" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A21" s="248"/>
-      <c r="B21" s="251"/>
+      <c r="A21" s="267"/>
+      <c r="B21" s="276"/>
       <c r="C21" s="46" t="s">
         <v>17</v>
       </c>
@@ -12564,10 +12564,10 @@
       <c r="AC21" s="20"/>
     </row>
     <row r="22" spans="1:31" s="6" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A22" s="252" t="s">
+      <c r="A22" s="254" t="s">
         <v>141</v>
       </c>
-      <c r="B22" s="249" t="s">
+      <c r="B22" s="274" t="s">
         <v>142</v>
       </c>
       <c r="C22" s="38" t="s">
@@ -12624,8 +12624,8 @@
       <c r="AC22" s="20"/>
     </row>
     <row r="23" spans="1:31" s="6" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A23" s="253"/>
-      <c r="B23" s="250"/>
+      <c r="A23" s="255"/>
+      <c r="B23" s="275"/>
       <c r="C23" s="40" t="s">
         <v>16</v>
       </c>
@@ -12681,8 +12681,8 @@
       <c r="AC23" s="20"/>
     </row>
     <row r="24" spans="1:31" s="6" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A24" s="254"/>
-      <c r="B24" s="251"/>
+      <c r="A24" s="256"/>
+      <c r="B24" s="276"/>
       <c r="C24" s="46" t="s">
         <v>17</v>
       </c>
@@ -12750,10 +12750,10 @@
       <c r="AC24" s="20"/>
     </row>
     <row r="25" spans="1:31" s="6" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A25" s="252" t="s">
+      <c r="A25" s="254" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="250"/>
+      <c r="B25" s="275"/>
       <c r="C25" s="38" t="s">
         <v>15</v>
       </c>
@@ -12809,8 +12809,8 @@
       <c r="AC25" s="20"/>
     </row>
     <row r="26" spans="1:31" s="6" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A26" s="253"/>
-      <c r="B26" s="250"/>
+      <c r="A26" s="255"/>
+      <c r="B26" s="275"/>
       <c r="C26" s="40" t="s">
         <v>16</v>
       </c>
@@ -12868,8 +12868,8 @@
       <c r="AE26" s="197"/>
     </row>
     <row r="27" spans="1:31" s="6" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A27" s="254"/>
-      <c r="B27" s="251"/>
+      <c r="A27" s="256"/>
+      <c r="B27" s="276"/>
       <c r="C27" s="46" t="s">
         <v>17</v>
       </c>
@@ -12939,10 +12939,10 @@
       <c r="AE27" s="197"/>
     </row>
     <row r="28" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A28" s="269" t="s">
+      <c r="A28" s="268" t="s">
         <v>158</v>
       </c>
-      <c r="B28" s="242" t="s">
+      <c r="B28" s="251" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="41" t="s">
@@ -13003,8 +13003,8 @@
       <c r="AE28" s="197"/>
     </row>
     <row r="29" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A29" s="270"/>
-      <c r="B29" s="243"/>
+      <c r="A29" s="269"/>
+      <c r="B29" s="252"/>
       <c r="C29" s="28" t="s">
         <v>16</v>
       </c>
@@ -13063,8 +13063,8 @@
       <c r="AE29" s="197"/>
     </row>
     <row r="30" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A30" s="271"/>
-      <c r="B30" s="244"/>
+      <c r="A30" s="270"/>
+      <c r="B30" s="253"/>
       <c r="C30" s="46" t="s">
         <v>17</v>
       </c>
@@ -13135,10 +13135,10 @@
       <c r="AE30" s="197"/>
     </row>
     <row r="31" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A31" s="269" t="s">
+      <c r="A31" s="268" t="s">
         <v>163</v>
       </c>
-      <c r="B31" s="242" t="s">
+      <c r="B31" s="251" t="s">
         <v>164</v>
       </c>
       <c r="C31" s="41" t="s">
@@ -13199,8 +13199,8 @@
       <c r="AE31" s="197"/>
     </row>
     <row r="32" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A32" s="270"/>
-      <c r="B32" s="243"/>
+      <c r="A32" s="269"/>
+      <c r="B32" s="252"/>
       <c r="C32" s="28" t="s">
         <v>16</v>
       </c>
@@ -13257,8 +13257,8 @@
       <c r="AE32" s="197"/>
     </row>
     <row r="33" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A33" s="271"/>
-      <c r="B33" s="244"/>
+      <c r="A33" s="270"/>
+      <c r="B33" s="253"/>
       <c r="C33" s="46" t="s">
         <v>17</v>
       </c>
@@ -13329,10 +13329,10 @@
       <c r="AE33" s="197"/>
     </row>
     <row r="34" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A34" s="272" t="s">
+      <c r="A34" s="277" t="s">
         <v>174</v>
       </c>
-      <c r="B34" s="242" t="s">
+      <c r="B34" s="251" t="s">
         <v>173</v>
       </c>
       <c r="C34" s="41" t="s">
@@ -13393,8 +13393,8 @@
       <c r="AE34" s="197"/>
     </row>
     <row r="35" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A35" s="273"/>
-      <c r="B35" s="243"/>
+      <c r="A35" s="278"/>
+      <c r="B35" s="252"/>
       <c r="C35" s="28" t="s">
         <v>16</v>
       </c>
@@ -13453,8 +13453,8 @@
       <c r="AE35" s="197"/>
     </row>
     <row r="36" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A36" s="274"/>
-      <c r="B36" s="244"/>
+      <c r="A36" s="279"/>
+      <c r="B36" s="253"/>
       <c r="C36" s="46" t="s">
         <v>17</v>
       </c>
@@ -13525,10 +13525,10 @@
       <c r="AE36" s="197"/>
     </row>
     <row r="37" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A37" s="258" t="s">
+      <c r="A37" s="263" t="s">
         <v>155</v>
       </c>
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="252" t="s">
         <v>45</v>
       </c>
       <c r="C37" s="41" t="s">
@@ -13589,8 +13589,8 @@
       <c r="AE37" s="197"/>
     </row>
     <row r="38" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A38" s="247"/>
-      <c r="B38" s="243"/>
+      <c r="A38" s="264"/>
+      <c r="B38" s="252"/>
       <c r="C38" s="28" t="s">
         <v>16</v>
       </c>
@@ -13648,8 +13648,8 @@
       <c r="AE38" s="197"/>
     </row>
     <row r="39" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A39" s="259"/>
-      <c r="B39" s="243"/>
+      <c r="A39" s="265"/>
+      <c r="B39" s="252"/>
       <c r="C39" s="46" t="s">
         <v>17</v>
       </c>
@@ -13720,10 +13720,10 @@
       <c r="AE39" s="197"/>
     </row>
     <row r="40" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A40" s="246" t="s">
+      <c r="A40" s="266" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="267" t="s">
+      <c r="B40" s="271" t="s">
         <v>44</v>
       </c>
       <c r="C40" s="33" t="s">
@@ -13784,8 +13784,8 @@
       <c r="AE40" s="197"/>
     </row>
     <row r="41" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A41" s="247"/>
-      <c r="B41" s="245"/>
+      <c r="A41" s="264"/>
+      <c r="B41" s="272"/>
       <c r="C41" s="36" t="s">
         <v>16</v>
       </c>
@@ -13844,8 +13844,8 @@
       <c r="AE41" s="197"/>
     </row>
     <row r="42" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A42" s="248"/>
-      <c r="B42" s="268"/>
+      <c r="A42" s="267"/>
+      <c r="B42" s="273"/>
       <c r="C42" s="46" t="s">
         <v>17</v>
       </c>
@@ -13916,10 +13916,10 @@
       <c r="AE42" s="197"/>
     </row>
     <row r="43" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A43" s="258" t="s">
+      <c r="A43" s="263" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="243" t="s">
+      <c r="B43" s="252" t="s">
         <v>41</v>
       </c>
       <c r="C43" s="41" t="s">
@@ -13980,8 +13980,8 @@
       <c r="AE43" s="197"/>
     </row>
     <row r="44" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A44" s="247"/>
-      <c r="B44" s="243"/>
+      <c r="A44" s="264"/>
+      <c r="B44" s="252"/>
       <c r="C44" s="28" t="s">
         <v>16</v>
       </c>
@@ -14040,8 +14040,8 @@
       <c r="AE44" s="197"/>
     </row>
     <row r="45" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A45" s="259"/>
-      <c r="B45" s="243"/>
+      <c r="A45" s="265"/>
+      <c r="B45" s="252"/>
       <c r="C45" s="46" t="s">
         <v>17</v>
       </c>
@@ -14112,10 +14112,10 @@
       <c r="AE45" s="197"/>
     </row>
     <row r="46" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A46" s="269" t="s">
+      <c r="A46" s="268" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="242" t="s">
+      <c r="B46" s="251" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="41" t="s">
@@ -14176,8 +14176,8 @@
       <c r="AE46" s="197"/>
     </row>
     <row r="47" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A47" s="270"/>
-      <c r="B47" s="243"/>
+      <c r="A47" s="269"/>
+      <c r="B47" s="252"/>
       <c r="C47" s="28" t="s">
         <v>16</v>
       </c>
@@ -14236,8 +14236,8 @@
       <c r="AE47" s="197"/>
     </row>
     <row r="48" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A48" s="271"/>
-      <c r="B48" s="244"/>
+      <c r="A48" s="270"/>
+      <c r="B48" s="253"/>
       <c r="C48" s="46" t="s">
         <v>17</v>
       </c>
@@ -14308,10 +14308,10 @@
       <c r="AE48" s="197"/>
     </row>
     <row r="49" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="268" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="249" t="s">
+      <c r="B49" s="274" t="s">
         <v>152</v>
       </c>
       <c r="C49" s="38" t="s">
@@ -14372,8 +14372,8 @@
       <c r="AE49" s="197"/>
     </row>
     <row r="50" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A50" s="270"/>
-      <c r="B50" s="250"/>
+      <c r="A50" s="269"/>
+      <c r="B50" s="275"/>
       <c r="C50" s="40" t="s">
         <v>16</v>
       </c>
@@ -14432,8 +14432,8 @@
       <c r="AE50" s="197"/>
     </row>
     <row r="51" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A51" s="271"/>
-      <c r="B51" s="251"/>
+      <c r="A51" s="270"/>
+      <c r="B51" s="276"/>
       <c r="C51" s="46" t="s">
         <v>17</v>
       </c>
@@ -14501,10 +14501,10 @@
       <c r="AB51"/>
     </row>
     <row r="52" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A52" s="255" t="s">
+      <c r="A52" s="283" t="s">
         <v>171</v>
       </c>
-      <c r="B52" s="245" t="s">
+      <c r="B52" s="272" t="s">
         <v>172</v>
       </c>
       <c r="C52" s="41" t="s">
@@ -14562,8 +14562,8 @@
       <c r="AB52"/>
     </row>
     <row r="53" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A53" s="256"/>
-      <c r="B53" s="245"/>
+      <c r="A53" s="284"/>
+      <c r="B53" s="272"/>
       <c r="C53" s="28" t="s">
         <v>16</v>
       </c>
@@ -14619,8 +14619,8 @@
       <c r="AB53"/>
     </row>
     <row r="54" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A54" s="257"/>
-      <c r="B54" s="245"/>
+      <c r="A54" s="285"/>
+      <c r="B54" s="272"/>
       <c r="C54" s="46" t="s">
         <v>17</v>
       </c>
@@ -14688,10 +14688,10 @@
       <c r="AB54"/>
     </row>
     <row r="55" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A55" s="246" t="s">
+      <c r="A55" s="266" t="s">
         <v>167</v>
       </c>
-      <c r="B55" s="242" t="s">
+      <c r="B55" s="251" t="s">
         <v>168</v>
       </c>
       <c r="C55" s="41" t="s">
@@ -14749,8 +14749,8 @@
       <c r="AB55"/>
     </row>
     <row r="56" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A56" s="247"/>
-      <c r="B56" s="243"/>
+      <c r="A56" s="264"/>
+      <c r="B56" s="252"/>
       <c r="C56" s="28" t="s">
         <v>16</v>
       </c>
@@ -14805,8 +14805,8 @@
       <c r="AA56" s="208"/>
     </row>
     <row r="57" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A57" s="248"/>
-      <c r="B57" s="244"/>
+      <c r="A57" s="267"/>
+      <c r="B57" s="253"/>
       <c r="C57" s="46" t="s">
         <v>17</v>
       </c>
@@ -14873,10 +14873,10 @@
       <c r="AA57" s="207"/>
     </row>
     <row r="58" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A58" s="258" t="s">
+      <c r="A58" s="263" t="s">
         <v>165</v>
       </c>
-      <c r="B58" s="242" t="s">
+      <c r="B58" s="251" t="s">
         <v>166</v>
       </c>
       <c r="C58" s="41" t="s">
@@ -14933,8 +14933,8 @@
       <c r="AA58" s="207"/>
     </row>
     <row r="59" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A59" s="247"/>
-      <c r="B59" s="243"/>
+      <c r="A59" s="264"/>
+      <c r="B59" s="252"/>
       <c r="C59" s="28" t="s">
         <v>16</v>
       </c>
@@ -14989,8 +14989,8 @@
       <c r="AA59" s="207"/>
     </row>
     <row r="60" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A60" s="259"/>
-      <c r="B60" s="244"/>
+      <c r="A60" s="265"/>
+      <c r="B60" s="253"/>
       <c r="C60" s="46" t="s">
         <v>17</v>
       </c>
@@ -15057,10 +15057,10 @@
       <c r="AA60" s="207"/>
     </row>
     <row r="61" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A61" s="260" t="s">
+      <c r="A61" s="286" t="s">
         <v>47</v>
       </c>
-      <c r="B61" s="243" t="s">
+      <c r="B61" s="252" t="s">
         <v>48</v>
       </c>
       <c r="C61" s="41" t="s">
@@ -15117,8 +15117,8 @@
       <c r="AA61" s="207"/>
     </row>
     <row r="62" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A62" s="261"/>
-      <c r="B62" s="243"/>
+      <c r="A62" s="287"/>
+      <c r="B62" s="252"/>
       <c r="C62" s="28" t="s">
         <v>16</v>
       </c>
@@ -15173,8 +15173,8 @@
       <c r="AA62" s="207"/>
     </row>
     <row r="63" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A63" s="262"/>
-      <c r="B63" s="243"/>
+      <c r="A63" s="288"/>
+      <c r="B63" s="252"/>
       <c r="C63" s="46" t="s">
         <v>17</v>
       </c>
@@ -15241,10 +15241,10 @@
       <c r="AA63" s="208"/>
     </row>
     <row r="64" spans="1:31" ht="13.5" customHeight="1">
-      <c r="A64" s="239" t="s">
+      <c r="A64" s="248" t="s">
         <v>179</v>
       </c>
-      <c r="B64" s="263" t="s">
+      <c r="B64" s="289" t="s">
         <v>156</v>
       </c>
       <c r="C64" s="41" t="s">
@@ -15301,8 +15301,8 @@
       <c r="AA64" s="20"/>
     </row>
     <row r="65" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A65" s="240"/>
-      <c r="B65" s="250"/>
+      <c r="A65" s="249"/>
+      <c r="B65" s="275"/>
       <c r="C65" s="28" t="s">
         <v>16</v>
       </c>
@@ -15357,8 +15357,8 @@
       <c r="AA65" s="6"/>
     </row>
     <row r="66" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A66" s="241"/>
-      <c r="B66" s="251"/>
+      <c r="A66" s="250"/>
+      <c r="B66" s="276"/>
       <c r="C66" s="46" t="s">
         <v>17</v>
       </c>
@@ -15416,10 +15416,10 @@
       </c>
     </row>
     <row r="67" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A67" s="233" t="s">
+      <c r="A67" s="245" t="s">
         <v>176</v>
       </c>
-      <c r="B67" s="249" t="s">
+      <c r="B67" s="274" t="s">
         <v>177</v>
       </c>
       <c r="C67" s="41" t="s">
@@ -15467,8 +15467,8 @@
       </c>
     </row>
     <row r="68" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A68" s="234"/>
-      <c r="B68" s="250"/>
+      <c r="A68" s="246"/>
+      <c r="B68" s="275"/>
       <c r="C68" s="28" t="s">
         <v>16</v>
       </c>
@@ -15514,8 +15514,8 @@
       </c>
     </row>
     <row r="69" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A69" s="235"/>
-      <c r="B69" s="251"/>
+      <c r="A69" s="247"/>
+      <c r="B69" s="276"/>
       <c r="C69" s="46" t="s">
         <v>17</v>
       </c>
@@ -15573,10 +15573,10 @@
       </c>
     </row>
     <row r="70" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A70" s="252" t="s">
+      <c r="A70" s="254" t="s">
         <v>137</v>
       </c>
-      <c r="B70" s="242" t="s">
+      <c r="B70" s="251" t="s">
         <v>139</v>
       </c>
       <c r="C70" s="41" t="s">
@@ -15633,8 +15633,8 @@
       <c r="AA70" s="207"/>
     </row>
     <row r="71" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A71" s="253"/>
-      <c r="B71" s="243"/>
+      <c r="A71" s="255"/>
+      <c r="B71" s="252"/>
       <c r="C71" s="28" t="s">
         <v>16</v>
       </c>
@@ -15689,8 +15689,8 @@
       <c r="AA71" s="207"/>
     </row>
     <row r="72" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A72" s="254"/>
-      <c r="B72" s="244"/>
+      <c r="A72" s="256"/>
+      <c r="B72" s="253"/>
       <c r="C72" s="46" t="s">
         <v>17</v>
       </c>
@@ -15757,10 +15757,10 @@
       <c r="AA72" s="207"/>
     </row>
     <row r="73" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A73" s="252" t="s">
+      <c r="A73" s="254" t="s">
         <v>138</v>
       </c>
-      <c r="B73" s="242" t="s">
+      <c r="B73" s="251" t="s">
         <v>140</v>
       </c>
       <c r="C73" s="41" t="s">
@@ -15817,8 +15817,8 @@
       <c r="AA73" s="207"/>
     </row>
     <row r="74" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A74" s="253"/>
-      <c r="B74" s="243"/>
+      <c r="A74" s="255"/>
+      <c r="B74" s="252"/>
       <c r="C74" s="28" t="s">
         <v>16</v>
       </c>
@@ -15873,8 +15873,8 @@
       <c r="AA74" s="207"/>
     </row>
     <row r="75" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A75" s="254"/>
-      <c r="B75" s="244"/>
+      <c r="A75" s="256"/>
+      <c r="B75" s="253"/>
       <c r="C75" s="46" t="s">
         <v>17</v>
       </c>
@@ -15941,10 +15941,10 @@
       <c r="AA75" s="207"/>
     </row>
     <row r="76" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A76" s="278" t="s">
+      <c r="A76" s="257" t="s">
         <v>144</v>
       </c>
-      <c r="B76" s="242" t="s">
+      <c r="B76" s="251" t="s">
         <v>145</v>
       </c>
       <c r="C76" s="41" t="s">
@@ -16001,8 +16001,8 @@
       <c r="AA76" s="207"/>
     </row>
     <row r="77" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A77" s="279"/>
-      <c r="B77" s="243"/>
+      <c r="A77" s="258"/>
+      <c r="B77" s="252"/>
       <c r="C77" s="28" t="s">
         <v>16</v>
       </c>
@@ -16057,8 +16057,8 @@
       <c r="AA77" s="207"/>
     </row>
     <row r="78" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A78" s="280"/>
-      <c r="B78" s="244"/>
+      <c r="A78" s="259"/>
+      <c r="B78" s="253"/>
       <c r="C78" s="46" t="s">
         <v>17</v>
       </c>
@@ -16125,10 +16125,10 @@
       <c r="AA78" s="207"/>
     </row>
     <row r="79" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A79" s="252" t="s">
+      <c r="A79" s="254" t="s">
         <v>146</v>
       </c>
-      <c r="B79" s="242" t="s">
+      <c r="B79" s="251" t="s">
         <v>147</v>
       </c>
       <c r="C79" s="41" t="s">
@@ -16185,8 +16185,8 @@
       <c r="AA79" s="207"/>
     </row>
     <row r="80" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A80" s="253"/>
-      <c r="B80" s="243"/>
+      <c r="A80" s="255"/>
+      <c r="B80" s="252"/>
       <c r="C80" s="28" t="s">
         <v>16</v>
       </c>
@@ -16241,8 +16241,8 @@
       <c r="AA80" s="207"/>
     </row>
     <row r="81" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A81" s="254"/>
-      <c r="B81" s="244"/>
+      <c r="A81" s="256"/>
+      <c r="B81" s="253"/>
       <c r="C81" s="46" t="s">
         <v>17</v>
       </c>
@@ -16309,10 +16309,10 @@
       <c r="AA81" s="207"/>
     </row>
     <row r="82" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A82" s="246" t="s">
+      <c r="A82" s="266" t="s">
         <v>50</v>
       </c>
-      <c r="B82" s="242" t="s">
+      <c r="B82" s="251" t="s">
         <v>49</v>
       </c>
       <c r="C82" s="41" t="s">
@@ -16369,8 +16369,8 @@
       <c r="AA82" s="207"/>
     </row>
     <row r="83" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A83" s="247"/>
-      <c r="B83" s="243"/>
+      <c r="A83" s="264"/>
+      <c r="B83" s="252"/>
       <c r="C83" s="28" t="s">
         <v>16</v>
       </c>
@@ -16425,8 +16425,8 @@
       <c r="AA83" s="208"/>
     </row>
     <row r="84" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A84" s="248"/>
-      <c r="B84" s="244"/>
+      <c r="A84" s="267"/>
+      <c r="B84" s="253"/>
       <c r="C84" s="46" t="s">
         <v>17</v>
       </c>
@@ -16493,10 +16493,10 @@
       <c r="AA84" s="208"/>
     </row>
     <row r="85" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A85" s="239" t="s">
+      <c r="A85" s="248" t="s">
         <v>148</v>
       </c>
-      <c r="B85" s="242" t="s">
+      <c r="B85" s="251" t="s">
         <v>149</v>
       </c>
       <c r="C85" s="41" t="s">
@@ -16551,8 +16551,8 @@
       <c r="Y85" s="195"/>
     </row>
     <row r="86" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A86" s="240"/>
-      <c r="B86" s="243"/>
+      <c r="A86" s="249"/>
+      <c r="B86" s="252"/>
       <c r="C86" s="28" t="s">
         <v>16</v>
       </c>
@@ -16605,8 +16605,8 @@
       <c r="Y86" s="195"/>
     </row>
     <row r="87" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A87" s="241"/>
-      <c r="B87" s="244"/>
+      <c r="A87" s="250"/>
+      <c r="B87" s="253"/>
       <c r="C87" s="46" t="s">
         <v>17</v>
       </c>
@@ -16671,10 +16671,10 @@
       <c r="Y87" s="1"/>
     </row>
     <row r="88" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A88" s="239" t="s">
+      <c r="A88" s="248" t="s">
         <v>160</v>
       </c>
-      <c r="B88" s="242" t="s">
+      <c r="B88" s="251" t="s">
         <v>161</v>
       </c>
       <c r="C88" s="41" t="s">
@@ -16722,8 +16722,8 @@
       </c>
     </row>
     <row r="89" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A89" s="240"/>
-      <c r="B89" s="243"/>
+      <c r="A89" s="249"/>
+      <c r="B89" s="252"/>
       <c r="C89" s="28" t="s">
         <v>16</v>
       </c>
@@ -16769,8 +16769,8 @@
       </c>
     </row>
     <row r="90" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A90" s="241"/>
-      <c r="B90" s="244"/>
+      <c r="A90" s="250"/>
+      <c r="B90" s="253"/>
       <c r="C90" s="46" t="s">
         <v>17</v>
       </c>
@@ -16828,10 +16828,10 @@
       </c>
     </row>
     <row r="91" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A91" s="239" t="s">
+      <c r="A91" s="248" t="s">
         <v>150</v>
       </c>
-      <c r="B91" s="242" t="s">
+      <c r="B91" s="251" t="s">
         <v>151</v>
       </c>
       <c r="C91" s="41" t="s">
@@ -16879,8 +16879,8 @@
       </c>
     </row>
     <row r="92" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A92" s="240"/>
-      <c r="B92" s="243"/>
+      <c r="A92" s="249"/>
+      <c r="B92" s="252"/>
       <c r="C92" s="28" t="s">
         <v>16</v>
       </c>
@@ -16926,8 +16926,8 @@
       </c>
     </row>
     <row r="93" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A93" s="241"/>
-      <c r="B93" s="244"/>
+      <c r="A93" s="250"/>
+      <c r="B93" s="253"/>
       <c r="C93" s="46" t="s">
         <v>17</v>
       </c>
@@ -16985,10 +16985,10 @@
       </c>
     </row>
     <row r="94" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A94" s="239" t="s">
+      <c r="A94" s="248" t="s">
         <v>169</v>
       </c>
-      <c r="B94" s="242" t="s">
+      <c r="B94" s="251" t="s">
         <v>170</v>
       </c>
       <c r="C94" s="41" t="s">
@@ -17036,8 +17036,8 @@
       </c>
     </row>
     <row r="95" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A95" s="240"/>
-      <c r="B95" s="243"/>
+      <c r="A95" s="249"/>
+      <c r="B95" s="252"/>
       <c r="C95" s="28" t="s">
         <v>16</v>
       </c>
@@ -17083,8 +17083,8 @@
       </c>
     </row>
     <row r="96" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A96" s="241"/>
-      <c r="B96" s="244"/>
+      <c r="A96" s="250"/>
+      <c r="B96" s="253"/>
       <c r="C96" s="46" t="s">
         <v>17</v>
       </c>
@@ -17142,10 +17142,10 @@
       </c>
     </row>
     <row r="97" spans="1:16" ht="13.5" customHeight="1">
-      <c r="A97" s="239" t="s">
+      <c r="A97" s="248" t="s">
         <v>175</v>
       </c>
-      <c r="B97" s="242" t="s">
+      <c r="B97" s="251" t="s">
         <v>157</v>
       </c>
       <c r="C97" s="41" t="s">
@@ -17193,8 +17193,8 @@
       </c>
     </row>
     <row r="98" spans="1:16" ht="13.5" customHeight="1">
-      <c r="A98" s="240"/>
-      <c r="B98" s="243"/>
+      <c r="A98" s="249"/>
+      <c r="B98" s="252"/>
       <c r="C98" s="28" t="s">
         <v>16</v>
       </c>
@@ -17240,8 +17240,8 @@
       </c>
     </row>
     <row r="99" spans="1:16" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A99" s="241"/>
-      <c r="B99" s="244"/>
+      <c r="A99" s="250"/>
+      <c r="B99" s="253"/>
       <c r="C99" s="224" t="s">
         <v>17</v>
       </c>
@@ -17299,10 +17299,10 @@
       </c>
     </row>
     <row r="100" spans="1:16" ht="13.5" customHeight="1">
-      <c r="A100" s="233" t="s">
+      <c r="A100" s="245" t="s">
         <v>162</v>
       </c>
-      <c r="B100" s="236" t="s">
+      <c r="B100" s="290" t="s">
         <v>178</v>
       </c>
       <c r="C100" s="228" t="s">
@@ -17350,8 +17350,8 @@
       </c>
     </row>
     <row r="101" spans="1:16" ht="13.5" customHeight="1">
-      <c r="A101" s="234"/>
-      <c r="B101" s="237"/>
+      <c r="A101" s="246"/>
+      <c r="B101" s="291"/>
       <c r="C101" s="229" t="s">
         <v>16</v>
       </c>
@@ -17397,9 +17397,9 @@
       </c>
     </row>
     <row r="102" spans="1:16" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A102" s="235"/>
-      <c r="B102" s="238"/>
-      <c r="C102" s="305" t="s">
+      <c r="A102" s="247"/>
+      <c r="B102" s="292"/>
+      <c r="C102" s="233" t="s">
         <v>17</v>
       </c>
       <c r="D102" s="225">
@@ -17450,128 +17450,128 @@
         <f t="shared" si="89"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P102" s="316">
+      <c r="P102" s="244">
         <f>P101/P100</f>
         <v>1.282051282051282E-2</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="13.5" customHeight="1">
-      <c r="A103" s="233" t="s">
+      <c r="A103" s="245" t="s">
         <v>180</v>
       </c>
-      <c r="B103" s="233" t="s">
+      <c r="B103" s="245" t="s">
         <v>181</v>
       </c>
-      <c r="C103" s="310" t="s">
+      <c r="C103" s="238" t="s">
         <v>15</v>
       </c>
-      <c r="D103" s="311">
-        <v>0</v>
-      </c>
-      <c r="E103" s="311">
-        <v>0</v>
-      </c>
-      <c r="F103" s="311">
+      <c r="D103" s="239">
+        <v>0</v>
+      </c>
+      <c r="E103" s="239">
+        <v>0</v>
+      </c>
+      <c r="F103" s="239">
         <v>2</v>
       </c>
-      <c r="G103" s="311"/>
-      <c r="H103" s="311"/>
-      <c r="I103" s="311"/>
-      <c r="J103" s="311"/>
-      <c r="K103" s="311"/>
-      <c r="L103" s="311"/>
-      <c r="M103" s="311"/>
-      <c r="N103" s="311"/>
-      <c r="O103" s="314"/>
-      <c r="P103" s="308">
+      <c r="G103" s="239"/>
+      <c r="H103" s="239"/>
+      <c r="I103" s="239"/>
+      <c r="J103" s="239"/>
+      <c r="K103" s="239"/>
+      <c r="L103" s="239"/>
+      <c r="M103" s="239"/>
+      <c r="N103" s="239"/>
+      <c r="O103" s="242"/>
+      <c r="P103" s="236">
         <f>SUM(D103:O103)</f>
         <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:16" ht="13.5" customHeight="1">
-      <c r="A104" s="234"/>
-      <c r="B104" s="234"/>
-      <c r="C104" s="312" t="s">
+      <c r="A104" s="246"/>
+      <c r="B104" s="246"/>
+      <c r="C104" s="240" t="s">
         <v>16</v>
       </c>
-      <c r="D104" s="306">
-        <v>0</v>
-      </c>
-      <c r="E104" s="306">
-        <v>0</v>
-      </c>
-      <c r="F104" s="306">
-        <v>0</v>
-      </c>
-      <c r="G104" s="306"/>
-      <c r="H104" s="306"/>
-      <c r="I104" s="306"/>
-      <c r="J104" s="306"/>
-      <c r="K104" s="306"/>
-      <c r="L104" s="306"/>
-      <c r="M104" s="306"/>
-      <c r="N104" s="306"/>
-      <c r="O104" s="307"/>
-      <c r="P104" s="309">
+      <c r="D104" s="234">
+        <v>0</v>
+      </c>
+      <c r="E104" s="234">
+        <v>0</v>
+      </c>
+      <c r="F104" s="234">
+        <v>0</v>
+      </c>
+      <c r="G104" s="234"/>
+      <c r="H104" s="234"/>
+      <c r="I104" s="234"/>
+      <c r="J104" s="234"/>
+      <c r="K104" s="234"/>
+      <c r="L104" s="234"/>
+      <c r="M104" s="234"/>
+      <c r="N104" s="234"/>
+      <c r="O104" s="235"/>
+      <c r="P104" s="237">
         <f>SUM(D104:O104)</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A105" s="235"/>
-      <c r="B105" s="235"/>
-      <c r="C105" s="313" t="s">
+      <c r="A105" s="247"/>
+      <c r="B105" s="247"/>
+      <c r="C105" s="241" t="s">
         <v>17</v>
       </c>
-      <c r="D105" s="315" t="e">
+      <c r="D105" s="243" t="e">
         <f>D104/D103</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E105" s="315" t="e">
+      <c r="E105" s="243" t="e">
         <f t="shared" ref="E105:P105" si="90">E104/E103</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F105" s="315">
+      <c r="F105" s="243">
         <f t="shared" si="90"/>
         <v>0</v>
       </c>
-      <c r="G105" s="315" t="e">
+      <c r="G105" s="243" t="e">
         <f t="shared" si="90"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H105" s="315" t="e">
+      <c r="H105" s="243" t="e">
         <f t="shared" si="90"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I105" s="315" t="e">
+      <c r="I105" s="243" t="e">
         <f t="shared" si="90"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J105" s="315" t="e">
+      <c r="J105" s="243" t="e">
         <f t="shared" si="90"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K105" s="315" t="e">
+      <c r="K105" s="243" t="e">
         <f t="shared" si="90"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L105" s="315" t="e">
+      <c r="L105" s="243" t="e">
         <f t="shared" si="90"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M105" s="315" t="e">
+      <c r="M105" s="243" t="e">
         <f t="shared" si="90"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N105" s="315" t="e">
+      <c r="N105" s="243" t="e">
         <f t="shared" si="90"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O105" s="315" t="e">
+      <c r="O105" s="243" t="e">
         <f t="shared" si="90"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P105" s="315">
+      <c r="P105" s="243">
         <f t="shared" si="90"/>
         <v>0</v>
       </c>
@@ -20236,22 +20236,31 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="A103:A105"/>
-    <mergeCell ref="B103:B105"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="A79:A81"/>
-    <mergeCell ref="A76:A78"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="A97:A99"/>
+    <mergeCell ref="B97:B99"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="A82:A84"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="A73:A75"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B25:B27"/>
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="A46:A48"/>
@@ -20268,28 +20277,22 @@
     <mergeCell ref="A34:A36"/>
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="A55:A57"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="A82:A84"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="A73:A75"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A103:A105"/>
+    <mergeCell ref="B103:B105"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="A79:A81"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="B79:B81"/>
     <mergeCell ref="A100:A102"/>
     <mergeCell ref="B100:B102"/>
     <mergeCell ref="A88:A90"/>
@@ -20297,9 +20300,6 @@
     <mergeCell ref="A94:A96"/>
     <mergeCell ref="B94:B96"/>
     <mergeCell ref="A91:A93"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="A97:A99"/>
-    <mergeCell ref="B97:B99"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="D23:O23">
@@ -21007,10 +21007,10 @@
       <c r="L4" s="73"/>
       <c r="M4" s="73"/>
       <c r="N4" s="73"/>
-      <c r="O4" s="297" t="s">
+      <c r="O4" s="293" t="s">
         <v>52</v>
       </c>
-      <c r="P4" s="297"/>
+      <c r="P4" s="293"/>
       <c r="Q4" s="75">
         <v>430</v>
       </c>
@@ -21087,7 +21087,7 @@
       <c r="AD5" s="84"/>
     </row>
     <row r="6" spans="1:32">
-      <c r="A6" s="298" t="s">
+      <c r="A6" s="294" t="s">
         <v>56</v>
       </c>
       <c r="B6" s="87" t="s">
@@ -21131,7 +21131,7 @@
       <c r="AD6" s="77"/>
     </row>
     <row r="7" spans="1:32">
-      <c r="A7" s="287"/>
+      <c r="A7" s="295"/>
       <c r="B7" s="93" t="s">
         <v>62</v>
       </c>
@@ -21173,7 +21173,7 @@
       <c r="AD7" s="77"/>
     </row>
     <row r="8" spans="1:32" ht="15.75" thickBot="1">
-      <c r="A8" s="288"/>
+      <c r="A8" s="296"/>
       <c r="B8" s="99" t="s">
         <v>65</v>
       </c>
@@ -21217,7 +21217,7 @@
       <c r="AF8" s="201"/>
     </row>
     <row r="9" spans="1:32" ht="15.75" thickBot="1">
-      <c r="A9" s="299" t="s">
+      <c r="A9" s="297" t="s">
         <v>68</v>
       </c>
       <c r="B9" s="101" t="s">
@@ -21263,11 +21263,11 @@
       <c r="AF9" s="201"/>
     </row>
     <row r="10" spans="1:32" ht="15">
-      <c r="A10" s="299"/>
+      <c r="A10" s="297"/>
       <c r="B10" s="93" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="289" t="s">
+      <c r="C10" s="299" t="s">
         <v>71</v>
       </c>
       <c r="D10" s="109" t="s">
@@ -21309,11 +21309,11 @@
       <c r="AF10" s="201"/>
     </row>
     <row r="11" spans="1:32" ht="15.75" thickBot="1">
-      <c r="A11" s="299"/>
+      <c r="A11" s="297"/>
       <c r="B11" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="290"/>
+      <c r="C11" s="300"/>
       <c r="D11" s="113" t="s">
         <v>74</v>
       </c>
@@ -21351,7 +21351,7 @@
       <c r="AF11" s="201"/>
     </row>
     <row r="12" spans="1:32" ht="15.75" thickBot="1">
-      <c r="A12" s="299"/>
+      <c r="A12" s="297"/>
       <c r="B12" s="118"/>
       <c r="C12" s="119" t="s">
         <v>76</v>
@@ -21391,7 +21391,7 @@
       <c r="AF12" s="201"/>
     </row>
     <row r="13" spans="1:32" ht="15">
-      <c r="A13" s="299"/>
+      <c r="A13" s="297"/>
       <c r="B13" s="87" t="s">
         <v>78</v>
       </c>
@@ -21437,7 +21437,7 @@
       <c r="AF13" s="201"/>
     </row>
     <row r="14" spans="1:32" ht="15.75" thickBot="1">
-      <c r="A14" s="299"/>
+      <c r="A14" s="297"/>
       <c r="B14" s="101" t="s">
         <v>83</v>
       </c>
@@ -21479,7 +21479,7 @@
       <c r="AF14" s="201"/>
     </row>
     <row r="15" spans="1:32" ht="15.75" thickBot="1">
-      <c r="A15" s="300"/>
+      <c r="A15" s="298"/>
       <c r="B15" s="101" t="s">
         <v>87</v>
       </c>
@@ -21521,13 +21521,13 @@
       <c r="AF15" s="201"/>
     </row>
     <row r="16" spans="1:32" ht="15">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="295" t="s">
         <v>90</v>
       </c>
       <c r="B16" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="289" t="s">
+      <c r="C16" s="299" t="s">
         <v>91</v>
       </c>
       <c r="D16" s="137" t="s">
@@ -21567,11 +21567,11 @@
       <c r="AF16" s="201"/>
     </row>
     <row r="17" spans="1:32" ht="15.75" thickBot="1">
-      <c r="A17" s="287"/>
+      <c r="A17" s="295"/>
       <c r="B17" s="107" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="290"/>
+      <c r="C17" s="300"/>
       <c r="D17" s="138" t="s">
         <v>74</v>
       </c>
@@ -21609,11 +21609,11 @@
       <c r="AF17" s="201"/>
     </row>
     <row r="18" spans="1:32" s="143" customFormat="1" ht="15">
-      <c r="A18" s="287"/>
+      <c r="A18" s="295"/>
       <c r="B18" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="291" t="s">
+      <c r="C18" s="311" t="s">
         <v>94</v>
       </c>
       <c r="D18" s="139" t="s">
@@ -21647,11 +21647,11 @@
       <c r="AF18" s="201"/>
     </row>
     <row r="19" spans="1:32" s="143" customFormat="1" ht="27.75" thickBot="1">
-      <c r="A19" s="287"/>
+      <c r="A19" s="295"/>
       <c r="B19" s="107" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="292"/>
+      <c r="C19" s="312"/>
       <c r="D19" s="144" t="s">
         <v>74</v>
       </c>
@@ -21683,11 +21683,11 @@
       <c r="AF19" s="201"/>
     </row>
     <row r="20" spans="1:32" ht="15">
-      <c r="A20" s="287"/>
+      <c r="A20" s="295"/>
       <c r="B20" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="293" t="s">
+      <c r="C20" s="313" t="s">
         <v>97</v>
       </c>
       <c r="D20" s="90" t="s">
@@ -21727,11 +21727,11 @@
       <c r="AF20" s="201"/>
     </row>
     <row r="21" spans="1:32" ht="15.75" thickBot="1">
-      <c r="A21" s="287"/>
+      <c r="A21" s="295"/>
       <c r="B21" s="101" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="294"/>
+      <c r="C21" s="314"/>
       <c r="D21" s="103" t="s">
         <v>74</v>
       </c>
@@ -21769,11 +21769,11 @@
       <c r="AF21" s="201"/>
     </row>
     <row r="22" spans="1:32" ht="15">
-      <c r="A22" s="287"/>
+      <c r="A22" s="295"/>
       <c r="B22" s="109" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="293" t="s">
+      <c r="C22" s="313" t="s">
         <v>102</v>
       </c>
       <c r="D22" s="154" t="s">
@@ -21813,11 +21813,11 @@
       <c r="AF22" s="201"/>
     </row>
     <row r="23" spans="1:32" ht="15.75" thickBot="1">
-      <c r="A23" s="287"/>
+      <c r="A23" s="295"/>
       <c r="B23" s="107" t="s">
         <v>104</v>
       </c>
-      <c r="C23" s="294"/>
+      <c r="C23" s="314"/>
       <c r="D23" s="120" t="s">
         <v>74</v>
       </c>
@@ -21855,11 +21855,11 @@
       <c r="AF23" s="201"/>
     </row>
     <row r="24" spans="1:32" ht="15">
-      <c r="A24" s="287"/>
+      <c r="A24" s="295"/>
       <c r="B24" s="93" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="295" t="s">
+      <c r="C24" s="315" t="s">
         <v>107</v>
       </c>
       <c r="D24" s="90" t="s">
@@ -21899,11 +21899,11 @@
       <c r="AF24" s="201"/>
     </row>
     <row r="25" spans="1:32" ht="15.75" thickBot="1">
-      <c r="A25" s="287"/>
+      <c r="A25" s="295"/>
       <c r="B25" s="101" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="296"/>
+      <c r="C25" s="316"/>
       <c r="D25" s="103" t="s">
         <v>74</v>
       </c>
@@ -21941,11 +21941,11 @@
       <c r="AF25" s="201"/>
     </row>
     <row r="26" spans="1:32">
-      <c r="A26" s="287"/>
+      <c r="A26" s="295"/>
       <c r="B26" s="93" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="293" t="s">
+      <c r="C26" s="313" t="s">
         <v>112</v>
       </c>
       <c r="D26" s="154" t="s">
@@ -21983,11 +21983,11 @@
       <c r="AD26" s="77"/>
     </row>
     <row r="27" spans="1:32" ht="14.25" thickBot="1">
-      <c r="A27" s="288"/>
+      <c r="A27" s="296"/>
       <c r="B27" s="107" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="294"/>
+      <c r="C27" s="314"/>
       <c r="D27" s="120" t="s">
         <v>74</v>
       </c>
@@ -22023,7 +22023,7 @@
       <c r="AD27" s="77"/>
     </row>
     <row r="28" spans="1:32">
-      <c r="A28" s="281" t="s">
+      <c r="A28" s="305" t="s">
         <v>116</v>
       </c>
       <c r="B28" s="167" t="s">
@@ -22032,7 +22032,7 @@
       <c r="C28" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D28" s="284" t="s">
+      <c r="D28" s="308" t="s">
         <v>59</v>
       </c>
       <c r="E28" s="168" t="s">
@@ -22079,14 +22079,14 @@
       </c>
     </row>
     <row r="29" spans="1:32">
-      <c r="A29" s="282"/>
+      <c r="A29" s="306"/>
       <c r="B29" s="170" t="s">
         <v>120</v>
       </c>
       <c r="C29" s="171" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="285"/>
+      <c r="D29" s="309"/>
       <c r="E29" s="171" t="s">
         <v>121</v>
       </c>
@@ -22103,7 +22103,7 @@
         <v>12870</v>
       </c>
       <c r="J29" s="190">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="K29" s="190">
         <v>0</v>
@@ -22132,14 +22132,14 @@
       <c r="V29" s="217"/>
     </row>
     <row r="30" spans="1:32" ht="14.25" thickBot="1">
-      <c r="A30" s="282"/>
+      <c r="A30" s="306"/>
       <c r="B30" s="173" t="s">
         <v>122</v>
       </c>
       <c r="C30" s="174" t="s">
         <v>159</v>
       </c>
-      <c r="D30" s="286"/>
+      <c r="D30" s="310"/>
       <c r="E30" s="175" t="s">
         <v>123</v>
       </c>
@@ -22156,7 +22156,7 @@
         <v>187021</v>
       </c>
       <c r="J30" s="191">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K30" s="191">
         <v>0</v>
@@ -22184,14 +22184,14 @@
       </c>
     </row>
     <row r="31" spans="1:32">
-      <c r="A31" s="282"/>
+      <c r="A31" s="306"/>
       <c r="B31" s="178" t="s">
         <v>124</v>
       </c>
       <c r="C31" s="179" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="285" t="s">
+      <c r="D31" s="309" t="s">
         <v>74</v>
       </c>
       <c r="E31" s="180" t="s">
@@ -22250,14 +22250,14 @@
       </c>
     </row>
     <row r="32" spans="1:32">
-      <c r="A32" s="282"/>
+      <c r="A32" s="306"/>
       <c r="B32" s="182" t="s">
         <v>127</v>
       </c>
       <c r="C32" s="171" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="285"/>
+      <c r="D32" s="309"/>
       <c r="E32" s="183" t="s">
         <v>129</v>
       </c>
@@ -22278,50 +22278,50 @@
       </c>
       <c r="J32" s="216">
         <f t="shared" si="2"/>
-        <v>29897</v>
+        <v>30210</v>
       </c>
       <c r="K32" s="216">
         <f t="shared" si="2"/>
-        <v>29897</v>
+        <v>30210</v>
       </c>
       <c r="L32" s="216">
         <f t="shared" si="2"/>
-        <v>29897</v>
+        <v>30210</v>
       </c>
       <c r="M32" s="216">
         <f t="shared" si="2"/>
-        <v>29897</v>
+        <v>30210</v>
       </c>
       <c r="N32" s="216">
         <f t="shared" si="2"/>
-        <v>29897</v>
+        <v>30210</v>
       </c>
       <c r="O32" s="216">
         <f t="shared" si="2"/>
-        <v>29897</v>
+        <v>30210</v>
       </c>
       <c r="P32" s="216">
         <f t="shared" si="2"/>
-        <v>29897</v>
+        <v>30210</v>
       </c>
       <c r="Q32" s="216">
         <f t="shared" si="2"/>
-        <v>29897</v>
+        <v>30210</v>
       </c>
       <c r="R32" s="216">
         <f t="shared" si="2"/>
-        <v>29897</v>
+        <v>30210</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="14.25" thickBot="1">
-      <c r="A33" s="283"/>
+      <c r="A33" s="307"/>
       <c r="B33" s="184" t="s">
         <v>130</v>
       </c>
       <c r="C33" s="174" t="s">
         <v>131</v>
       </c>
-      <c r="D33" s="286"/>
+      <c r="D33" s="310"/>
       <c r="E33" s="175" t="s">
         <v>132</v>
       </c>
@@ -22342,39 +22342,39 @@
       </c>
       <c r="J33" s="177">
         <f t="shared" si="2"/>
-        <v>467001</v>
+        <v>467013</v>
       </c>
       <c r="K33" s="177">
         <f t="shared" si="2"/>
-        <v>467001</v>
+        <v>467013</v>
       </c>
       <c r="L33" s="177">
         <f t="shared" si="2"/>
-        <v>467001</v>
+        <v>467013</v>
       </c>
       <c r="M33" s="177">
         <f t="shared" si="2"/>
-        <v>467001</v>
+        <v>467013</v>
       </c>
       <c r="N33" s="177">
         <f t="shared" si="2"/>
-        <v>467001</v>
+        <v>467013</v>
       </c>
       <c r="O33" s="177">
         <f t="shared" si="2"/>
-        <v>467001</v>
+        <v>467013</v>
       </c>
       <c r="P33" s="177">
         <f t="shared" si="2"/>
-        <v>467001</v>
+        <v>467013</v>
       </c>
       <c r="Q33" s="177">
         <f t="shared" si="2"/>
-        <v>467001</v>
+        <v>467013</v>
       </c>
       <c r="R33" s="177">
         <f t="shared" si="2"/>
-        <v>467001</v>
+        <v>467013</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -22402,12 +22402,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A9:A15"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
     <mergeCell ref="A28:A33"/>
     <mergeCell ref="D28:D30"/>
     <mergeCell ref="D31:D33"/>
@@ -22418,6 +22412,12 @@
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
     <mergeCell ref="C26:C27"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
